--- a/docs/StructureDefinition-space-adverse-event.xlsx
+++ b/docs/StructureDefinition-space-adverse-event.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-space-adverse-event.xlsx
+++ b/docs/StructureDefinition-space-adverse-event.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="296">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/space-adverse-event</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/space-adverse-event</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -447,7 +450,7 @@
     <t>missionContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/mission-context}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mission-context}
 </t>
   </si>
   <si>
@@ -467,7 +470,7 @@
     <t>flightDay</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://mitre.org/fhir/space-health/StructureDefinition/flight-day}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/flight-day}
 </t>
   </si>
   <si>
@@ -571,7 +574,7 @@
     <t>This element defines the specific type of event that occurred or that was prevented from occurring.</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/ValueSet/space-adverse-event-vs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/ValueSet/space-adverse-event-vs</t>
   </si>
   <si>
     <t>FiveWs.what[x]</t>
@@ -584,7 +587,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://mitre.org/fhir/space-health/StructureDefinition/Astronaut)
+    <t xml:space="preserve">Reference(https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/astronaut)
 </t>
   </si>
   <si>
@@ -1200,54 +1203,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1285,7 +1290,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="55.76171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.55859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="70.546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>
@@ -1301,137 +1306,137 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1443,13 +1448,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1500,33 +1505,33 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1534,10 +1539,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1546,19 +1551,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1608,13 +1613,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1631,10 +1636,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1642,10 +1647,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1654,16 +1659,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1714,19 +1719,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -1737,10 +1742,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1748,31 +1753,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1822,19 +1827,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -1845,10 +1850,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1856,10 +1861,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1871,16 +1876,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1906,13 +1911,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -1930,19 +1935,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -1953,21 +1958,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -1979,16 +1984,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2038,44 +2043,44 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2087,16 +2092,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2146,13 +2151,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2164,15 +2169,15 @@
         <v>20</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2180,10 +2185,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2195,13 +2200,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2240,29 +2245,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2273,26 +2278,26 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -2301,13 +2306,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2358,19 +2363,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2381,26 +2386,26 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>20</v>
@@ -2409,13 +2414,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2466,19 +2471,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -2489,45 +2494,45 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -2576,33 +2581,33 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2610,10 +2615,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -2622,22 +2627,22 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -2686,19 +2691,19 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>20</v>
@@ -2709,10 +2714,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2720,28 +2725,28 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2768,13 +2773,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -2792,22 +2797,22 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>20</v>
@@ -2815,10 +2820,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2826,10 +2831,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -2838,16 +2843,16 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2874,13 +2879,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -2898,22 +2903,22 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK15" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>20</v>
@@ -2921,10 +2926,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2932,28 +2937,28 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2980,11 +2985,11 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3002,22 +3007,22 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>20</v>
@@ -3025,45 +3030,45 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -3112,22 +3117,22 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>20</v>
@@ -3135,10 +3140,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3146,10 +3151,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -3158,19 +3163,19 @@
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3220,22 +3225,22 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>20</v>
@@ -3243,10 +3248,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3254,28 +3259,28 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3326,22 +3331,22 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>20</v>
@@ -3349,10 +3354,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3360,10 +3365,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -3372,16 +3377,16 @@
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3432,19 +3437,19 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>20</v>
@@ -3455,10 +3460,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3466,10 +3471,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -3478,19 +3483,19 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3540,22 +3545,22 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>20</v>
@@ -3563,10 +3568,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3574,10 +3579,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -3586,16 +3591,16 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3646,19 +3651,19 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
@@ -3669,10 +3674,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3680,10 +3685,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -3692,16 +3697,16 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3752,19 +3757,19 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
@@ -3775,10 +3780,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3786,28 +3791,28 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3834,13 +3839,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -3858,19 +3863,19 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -3881,10 +3886,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3892,10 +3897,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -3904,16 +3909,16 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3940,13 +3945,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -3964,19 +3969,19 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -3987,10 +3992,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3998,28 +4003,28 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4046,13 +4051,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4070,19 +4075,19 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
@@ -4093,10 +4098,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4104,10 +4109,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4116,16 +4121,16 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4176,22 +4181,22 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>20</v>
@@ -4199,10 +4204,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4210,10 +4215,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4222,16 +4227,16 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4282,19 +4287,19 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
@@ -4305,10 +4310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4316,28 +4321,28 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4388,19 +4393,19 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
@@ -4411,10 +4416,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4422,10 +4427,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -4437,13 +4442,13 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4494,13 +4499,13 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
@@ -4512,26 +4517,26 @@
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -4543,16 +4548,16 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4602,68 +4607,68 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -4712,62 +4717,62 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4818,19 +4823,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -4841,10 +4846,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4852,10 +4857,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -4864,16 +4869,16 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4924,19 +4929,19 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
@@ -4947,10 +4952,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4958,10 +4963,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -4973,13 +4978,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5030,13 +5035,13 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
@@ -5048,26 +5053,26 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -5079,16 +5084,16 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5138,68 +5143,68 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -5248,33 +5253,33 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5282,10 +5287,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -5294,16 +5299,16 @@
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5330,13 +5335,13 @@
         <v>20</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>20</v>
@@ -5354,19 +5359,19 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -5377,10 +5382,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5388,10 +5393,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -5400,16 +5405,16 @@
         <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5460,19 +5465,19 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -5483,10 +5488,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5494,10 +5499,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -5506,16 +5511,16 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5566,19 +5571,19 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
@@ -5589,10 +5594,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5600,10 +5605,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -5612,16 +5617,16 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5648,13 +5653,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -5672,19 +5677,19 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -5695,10 +5700,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5706,10 +5711,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -5718,16 +5723,16 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="L42" t="s" s="2">
-        <v>286</v>
-      </c>
       <c r="M42" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5778,19 +5783,19 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
@@ -5801,10 +5806,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5812,10 +5817,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -5824,16 +5829,16 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L43" t="s" s="2">
-        <v>289</v>
-      </c>
       <c r="M43" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5884,19 +5889,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -5907,10 +5912,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5918,10 +5923,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -5930,16 +5935,16 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="L44" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="M44" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5990,19 +5995,19 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
